--- a/Python Program list.xlsx
+++ b/Python Program list.xlsx
@@ -1,25 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://hpe-my.sharepoint.com/personal/rohit-kumar_mishra-ext_hpe_com/Documents/Git/Python_Practice/Pythonpractice/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="83" documentId="8_{4E7513DC-9981-44ED-A24B-5F88D7F78904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B7F4C9FF-9872-4A81-A624-C9B3D1EACC6B}"/>
+  <xr:revisionPtr revIDLastSave="154" documentId="8_{4E7513DC-9981-44ED-A24B-5F88D7F78904}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CA56DB8E-59C0-4479-90DD-EF41516BD09E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="2" xr2:uid="{AEEA7CD8-05C3-4443-BFD2-CDA2E2DA16FB}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" firstSheet="1" activeTab="4" xr2:uid="{AEEA7CD8-05C3-4443-BFD2-CDA2E2DA16FB}"/>
   </bookViews>
   <sheets>
     <sheet name="Program Name" sheetId="1" r:id="rId1"/>
     <sheet name="another Program List" sheetId="2" r:id="rId2"/>
-    <sheet name="Python Questions" sheetId="3" r:id="rId3"/>
-    <sheet name="List_Set_Tuple_Dictionary" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet1" sheetId="5" r:id="rId3"/>
+    <sheet name="Allure_tags" sheetId="6" r:id="rId4"/>
+    <sheet name="Python Questions" sheetId="3" r:id="rId5"/>
+    <sheet name="List_Set_Tuple_Dictionary" sheetId="4" r:id="rId6"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -40,7 +41,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="793" uniqueCount="665">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="853" uniqueCount="718">
   <si>
     <t>1. Data Types</t>
   </si>
@@ -1922,8 +1923,23 @@
     <t>Faster than list (due to immutability)</t>
   </si>
   <si>
-    <r>
-      <t>Faster membership testing (</t>
+    <t>Duplicates Handling</t>
+  </si>
+  <si>
+    <t>Allows duplicates</t>
+  </si>
+  <si>
+    <t>Removes duplicates automatically</t>
+  </si>
+  <si>
+    <t>Keys are unique; values can be duplicates</t>
+  </si>
+  <si>
+    <t>Usage Example</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Storing a list of items like </t>
     </r>
     <r>
       <rPr>
@@ -1931,7 +1947,69 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>O(1)</t>
+      <t>[1, 2, 3]</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Fixed data structure like coordinates </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>(1, 2, 3)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Unique items collection </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>{1, 2, 3}</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Key-value mapping </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>{'name': 'Alice', 'age': 25}</t>
+    </r>
+  </si>
+  <si>
+    <t>Similar Methods Among List, Tuple, Set, and Dictionary</t>
+  </si>
+  <si>
+    <t>Method</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>len()</t>
+  </si>
+  <si>
+    <t>✅</t>
+  </si>
+  <si>
+    <t>Returns the number of elements</t>
+  </si>
+  <si>
+    <r>
+      <t>in</t>
     </r>
     <r>
       <rPr>
@@ -1941,12 +2019,39 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>Faster lookups (</t>
+      <t xml:space="preserve"> (membership test)</t>
+    </r>
+  </si>
+  <si>
+    <t>Checks if an element/key exists</t>
+  </si>
+  <si>
+    <t>count()</t>
+  </si>
+  <si>
+    <t>❌</t>
+  </si>
+  <si>
+    <t>Returns occurrences of an element (List, Tuple)</t>
+  </si>
+  <si>
+    <t>index()</t>
+  </si>
+  <si>
+    <t>Returns index of an element (List, Tuple)</t>
+  </si>
+  <si>
+    <t>copy()</t>
+  </si>
+  <si>
+    <t>Returns a shallow copy</t>
+  </si>
+  <si>
+    <t>iteration</t>
+  </si>
+  <si>
+    <r>
+      <t>✅ (</t>
     </r>
     <r>
       <rPr>
@@ -1954,7 +2059,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>O(1)</t>
+      <t>for item in list1</t>
     </r>
     <r>
       <rPr>
@@ -1968,23 +2073,8 @@
     </r>
   </si>
   <si>
-    <t>Duplicates Handling</t>
-  </si>
-  <si>
-    <t>Allows duplicates</t>
-  </si>
-  <si>
-    <t>Removes duplicates automatically</t>
-  </si>
-  <si>
-    <t>Keys are unique; values can be duplicates</t>
-  </si>
-  <si>
-    <t>Usage Example</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Storing a list of items like </t>
+    <r>
+      <t>✅ (</t>
     </r>
     <r>
       <rPr>
@@ -1992,69 +2082,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>[1, 2, 3]</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Fixed data structure like coordinates </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>(1, 2, 3)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Unique items collection </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>{1, 2, 3}</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Key-value mapping </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>{'name': 'Alice', 'age': 25}</t>
-    </r>
-  </si>
-  <si>
-    <t>Similar Methods Among List, Tuple, Set, and Dictionary</t>
-  </si>
-  <si>
-    <t>Method</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>len()</t>
-  </si>
-  <si>
-    <t>✅</t>
-  </si>
-  <si>
-    <t>Returns the number of elements</t>
-  </si>
-  <si>
-    <r>
-      <t>in</t>
+      <t>for item in tuple1</t>
     </r>
     <r>
       <rPr>
@@ -2064,35 +2092,8 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> (membership test)</t>
-    </r>
-  </si>
-  <si>
-    <t>Checks if an element/key exists</t>
-  </si>
-  <si>
-    <t>count()</t>
-  </si>
-  <si>
-    <t>❌</t>
-  </si>
-  <si>
-    <t>Returns occurrences of an element (List, Tuple)</t>
-  </si>
-  <si>
-    <t>index()</t>
-  </si>
-  <si>
-    <t>Returns index of an element (List, Tuple)</t>
-  </si>
-  <si>
-    <t>copy()</t>
-  </si>
-  <si>
-    <t>Returns a shallow copy</t>
-  </si>
-  <si>
-    <t>iteration</t>
+      <t>)</t>
+    </r>
   </si>
   <si>
     <r>
@@ -2104,7 +2105,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>for item in list1</t>
+      <t>for item in set1</t>
     </r>
     <r>
       <rPr>
@@ -2127,7 +2128,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>for item in tuple1</t>
+      <t>for key in dict1</t>
     </r>
     <r>
       <rPr>
@@ -2141,8 +2142,29 @@
     </r>
   </si>
   <si>
-    <r>
-      <t>✅ (</t>
+    <t>Supports iteration</t>
+  </si>
+  <si>
+    <t>Unique Methods in Each Data Structure</t>
+  </si>
+  <si>
+    <t>append(x)</t>
+  </si>
+  <si>
+    <t>Adds an element to the end</t>
+  </si>
+  <si>
+    <t>extend(iterable)</t>
+  </si>
+  <si>
+    <t>Extends list with another iterable</t>
+  </si>
+  <si>
+    <t>insert(i, x)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Inserts </t>
     </r>
     <r>
       <rPr>
@@ -2150,7 +2172,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>for item in set1</t>
+      <t>x</t>
     </r>
     <r>
       <rPr>
@@ -2160,8 +2182,35 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)</t>
-    </r>
+      <t xml:space="preserve"> at index </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>i</t>
+    </r>
+  </si>
+  <si>
+    <t>remove(x)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Removes first occurrence of </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>x</t>
+    </r>
+  </si>
+  <si>
+    <t>pop(i)</t>
   </si>
   <si>
     <r>
@@ -2173,7 +2222,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>for key in dict1</t>
+      <t>pop()</t>
     </r>
     <r>
       <rPr>
@@ -2183,33 +2232,12 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>)</t>
-    </r>
-  </si>
-  <si>
-    <t>Supports iteration</t>
-  </si>
-  <si>
-    <t>Unique Methods in Each Data Structure</t>
-  </si>
-  <si>
-    <t>append(x)</t>
-  </si>
-  <si>
-    <t>Adds an element to the end</t>
-  </si>
-  <si>
-    <t>extend(iterable)</t>
-  </si>
-  <si>
-    <t>Extends list with another iterable</t>
-  </si>
-  <si>
-    <t>insert(i, x)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Inserts </t>
+      <t>, removes arbitrary item)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>✅ (</t>
     </r>
     <r>
       <rPr>
@@ -2217,7 +2245,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>x</t>
+      <t>pop(key)</t>
     </r>
     <r>
       <rPr>
@@ -2227,7 +2255,36 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> at index </t>
+      <t>, removes key-value pair)</t>
+    </r>
+  </si>
+  <si>
+    <t>Removes and returns element</t>
+  </si>
+  <si>
+    <t>sort()</t>
+  </si>
+  <si>
+    <t>Sorts the list in-place</t>
+  </si>
+  <si>
+    <t>reverse()</t>
+  </si>
+  <si>
+    <t>Reverses the list in-place</t>
+  </si>
+  <si>
+    <t>clear()</t>
+  </si>
+  <si>
+    <t>Removes all elements</t>
+  </si>
+  <si>
+    <t>add(x)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Adds </t>
     </r>
     <r>
       <rPr>
@@ -2235,39 +2292,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>i</t>
-    </r>
-  </si>
-  <si>
-    <t>remove(x)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Removes first occurrence of </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
       <t>x</t>
-    </r>
-  </si>
-  <si>
-    <t>pop(i)</t>
-  </si>
-  <si>
-    <r>
-      <t>✅ (</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Arial Unicode MS"/>
-      </rPr>
-      <t>pop()</t>
     </r>
     <r>
       <rPr>
@@ -2277,12 +2302,15 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>, removes arbitrary item)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>✅ (</t>
+      <t xml:space="preserve"> to the set</t>
+    </r>
+  </si>
+  <si>
+    <t>discard(x)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Removes </t>
     </r>
     <r>
       <rPr>
@@ -2290,7 +2318,7 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>pop(key)</t>
+      <t>x</t>
     </r>
     <r>
       <rPr>
@@ -2300,36 +2328,78 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>, removes key-value pair)</t>
-    </r>
-  </si>
-  <si>
-    <t>Removes and returns element</t>
-  </si>
-  <si>
-    <t>sort()</t>
-  </si>
-  <si>
-    <t>Sorts the list in-place</t>
-  </si>
-  <si>
-    <t>reverse()</t>
-  </si>
-  <si>
-    <t>Reverses the list in-place</t>
-  </si>
-  <si>
-    <t>clear()</t>
-  </si>
-  <si>
-    <t>Removes all elements</t>
-  </si>
-  <si>
-    <t>add(x)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Adds </t>
+      <t xml:space="preserve"> without error if absent</t>
+    </r>
+  </si>
+  <si>
+    <t>update(iterable)</t>
+  </si>
+  <si>
+    <t>Adds elements (Set) / Merges dicts (Dict)</t>
+  </si>
+  <si>
+    <t>union(set2)</t>
+  </si>
+  <si>
+    <t>Returns union of sets</t>
+  </si>
+  <si>
+    <t>intersection(set2)</t>
+  </si>
+  <si>
+    <t>Returns common elements between sets</t>
+  </si>
+  <si>
+    <t>difference(set2)</t>
+  </si>
+  <si>
+    <t>Returns elements unique to a set</t>
+  </si>
+  <si>
+    <t>symmetric_difference(set2)</t>
+  </si>
+  <si>
+    <t>Returns elements in either set but not both</t>
+  </si>
+  <si>
+    <t>keys()</t>
+  </si>
+  <si>
+    <t>Returns dictionary keys</t>
+  </si>
+  <si>
+    <t>values()</t>
+  </si>
+  <si>
+    <t>Returns dictionary values</t>
+  </si>
+  <si>
+    <t>items()</t>
+  </si>
+  <si>
+    <t>Returns key-value pairs</t>
+  </si>
+  <si>
+    <t>get(key, default)</t>
+  </si>
+  <si>
+    <t>Returns value for key, or default if missing</t>
+  </si>
+  <si>
+    <t>setdefault(key, default)</t>
+  </si>
+  <si>
+    <t>Sets key if not present</t>
+  </si>
+  <si>
+    <t>popitem()</t>
+  </si>
+  <si>
+    <t>Removes and returns a (key, value) pair</t>
+  </si>
+  <si>
+    <r>
+      <t>Faster membership testing (</t>
     </r>
     <r>
       <rPr>
@@ -2337,25 +2407,22 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>x</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> to the set</t>
-    </r>
-  </si>
-  <si>
-    <t>discard(x)</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Removes </t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Faster lookups (</t>
     </r>
     <r>
       <rPr>
@@ -2363,91 +2430,1003 @@
         <color theme="1"/>
         <rFont val="Arial Unicode MS"/>
       </rPr>
-      <t>x</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>O(1)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
         <color theme="1"/>
         <rFont val="Aptos Narrow"/>
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> without error if absent</t>
-    </r>
-  </si>
-  <si>
-    <t>update(iterable)</t>
-  </si>
-  <si>
-    <t>Adds elements (Set) / Merges dicts (Dict)</t>
-  </si>
-  <si>
-    <t>union(set2)</t>
-  </si>
-  <si>
-    <t>Returns union of sets</t>
-  </si>
-  <si>
-    <t>intersection(set2)</t>
-  </si>
-  <si>
-    <t>Returns common elements between sets</t>
-  </si>
-  <si>
-    <t>difference(set2)</t>
-  </si>
-  <si>
-    <t>Returns elements unique to a set</t>
-  </si>
-  <si>
-    <t>symmetric_difference(set2)</t>
-  </si>
-  <si>
-    <t>Returns elements in either set but not both</t>
-  </si>
-  <si>
-    <t>keys()</t>
-  </si>
-  <si>
-    <t>Returns dictionary keys</t>
-  </si>
-  <si>
-    <t>values()</t>
-  </si>
-  <si>
-    <t>Returns dictionary values</t>
-  </si>
-  <si>
-    <t>items()</t>
-  </si>
-  <si>
-    <t>Returns key-value pairs</t>
-  </si>
-  <si>
-    <t>get(key, default)</t>
-  </si>
-  <si>
-    <t>Returns value for key, or default if missing</t>
-  </si>
-  <si>
-    <t>setdefault(key, default)</t>
-  </si>
-  <si>
-    <t>Sets key if not present</t>
-  </si>
-  <si>
-    <t>popitem()</t>
-  </si>
-  <si>
-    <t>Removes and returns a (key, value) pair</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>done</t>
+  </si>
+  <si>
+    <t>Since you have 11.5 years of experience in the Telecom domain, you likely have strong knowledge of network elements, protocols, and testing methodologies. To align with market standards for Python API Testing Automation with reporting, here’s what you should prepare:</t>
+  </si>
+  <si>
+    <t>1. Core Python &amp; API Testing</t>
+  </si>
+  <si>
+    <r>
+      <t>Python Basics &amp; Advanced Concepts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (if not already familiar)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Requests Library</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for REST API interaction</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>json &amp; xml.etree.ElementTree</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for handling API responses</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>pytest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>unittest</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for API test case structuring</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>mocking &amp; patching</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> techniques for test isolation</t>
+    </r>
+  </si>
+  <si>
+    <t>2. API Automation Framework</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Understanding and implementing </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pytest-bdd</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for BDD-based testing</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Building </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>custom API testing frameworks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using Python</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Using </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>data-driven testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (parameterization)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>CI/CD Integration</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with Jenkins, GitHub Actions, or GitLab CI/CD</t>
+    </r>
+  </si>
+  <si>
+    <t>3. Reporting &amp; Logging</t>
+  </si>
+  <si>
+    <r>
+      <t>Allure Report</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>pytest-html</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for structured test reports</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Logging &amp; Debugging</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> using Python’s logging module</t>
+    </r>
+  </si>
+  <si>
+    <t>4. API Security &amp; Performance Testing</t>
+  </si>
+  <si>
+    <r>
+      <t>Security Testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Auth mechanisms: OAuth, JWT, Basic Auth)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Performance Testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Locust</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> or JMeter (since you already use JMeter)</t>
+    </r>
+  </si>
+  <si>
+    <t>5. Telecom-Specific Considerations</t>
+  </si>
+  <si>
+    <r>
+      <t>Protocol-Level Testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (SIP, Diameter, SS7, SOAP/XML APIs)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5G/4G Network Elements</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> testing</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Message Queues &amp; Kafka Testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> if applicable</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Database Testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (SQL, NoSQL) for mediation and charging systems</t>
+    </r>
+  </si>
+  <si>
+    <t>6. Industry &amp; DevOps Alignment</t>
+  </si>
+  <si>
+    <r>
+      <t>Containerization</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (Docker, Kubernetes)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Cloud API Testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> (AWS, Azure, GCP)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Postman</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> for quick API validation before automation</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Since you have telecom experience, focus on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>telecom API automation, security, and performance testing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> to stand out. Let me know if you need specific guidance on any of these areas! 🚀</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>title:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The primary name of the test or test suite, providing a concise summary. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.title("User Login Test")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>description:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A plain text description of the test, offering more detail than the title. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.description("Verifies user login with valid credentials.")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>description_html:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> An HTML-formatted description, allowing rich text and formatting. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.description_html("&lt;b&gt;Verifies user login&lt;/b&gt; with &lt;i&gt;valid credentials&lt;/i&gt;.")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>label:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Custom key-value pairs for categorizing and filtering tests. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.label("owner", "John Doe")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>severity:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Indicates the impact of a test failure (e.g., critical, normal, minor). Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.severity(allure.severity_level.CRITICAL)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>suite:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The logical grouping of tests within a test suite. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.suite("Authentication Suite")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>parent_suite:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> The higher-level suite containing the current suite. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.parent_suite("Regression Tests")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>sub_suite:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A finer-grained grouping within a suite. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.sub_suite("Valid Credentials")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>tag:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Keywords for filtering and organizing tests. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.tag("smoke", "login")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>id:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A unique identifier for the test case. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.id("TC-123")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>epic:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A high-level feature or project area. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.epic("User Management")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>feature:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A specific functionality within an epic. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.feature("Login Functionality")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>story:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A user story or specific scenario being tested. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.story("As a user, I can log in with valid credentials.")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>link:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A URL associated with the test (e.g., to a requirements document). Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.link("https://example.com/requirements/123", name="Requirement 123")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>issue:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A link to a bug tracking system issue. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.issue("BUG-456")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>testcase:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A link to a test case in a test management system. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.testcase("TMS-789")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>manual:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Indicates that the test was executed manually. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.manual()</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>step:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> A single action or verification within a test. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>with allure.step("Enter username"): ...</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>dynamic:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Allows adding elements to the report during test execution. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>allure.dynamic.title("Dynamic Title")</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>severity_level:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Enum representing the severity (e.g., CRITICAL, NORMAL, MINOR). Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>allure.severity_level.CRITICAL</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>attach:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Adds files or data to the report (e.g., screenshots, logs). Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>allure.attach(source="screenshot.png", name="Screenshot", attachment_type=allure.attachment_type.PNG)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>attachment_type:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Specifies the MIME type of an attachment. Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>allure.attachment_type.PNG</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>parameter_mode:</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> Specifies how parameters are displayed in the report (e.g., hidden, masked). Example: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>@allure.parameter("password", masked=True)</t>
+    </r>
+  </si>
+  <si>
+    <t>Difference Between Simultaneous Assignment and Sequential Assigments</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2482,6 +3461,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF1B1C1D"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -2497,7 +3497,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="11">
     <border>
       <left/>
       <right/>
@@ -2533,11 +3533,131 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -2594,6 +3714,46 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3136,11 +4296,17 @@
       <c r="A39" s="3" t="s">
         <v>27</v>
       </c>
+      <c r="B39" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="40" spans="1:2">
       <c r="A40" s="3" t="s">
         <v>28</v>
       </c>
+      <c r="B40" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="41" spans="1:2">
       <c r="A41" s="3" t="s">
@@ -3161,6 +4327,9 @@
       <c r="A44" s="3" t="s">
         <v>32</v>
       </c>
+      <c r="B44" t="s">
+        <v>41</v>
+      </c>
     </row>
     <row r="45" spans="1:2">
       <c r="A45" s="3" t="s">
@@ -3181,18 +4350,24 @@
       <c r="A48" s="3" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="49" spans="1:1">
+      <c r="B48" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
       <c r="A49" s="3" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="50" spans="1:1">
+      <c r="B49" t="s">
+        <v>665</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="A50" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="52" spans="1:1">
+    <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
         <v>39</v>
       </c>
@@ -3205,83 +4380,92 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5CEC6092-6325-4945-B949-EBA0DE546D9F}">
-  <dimension ref="A2:A526"/>
+  <dimension ref="A2:B526"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
     <col min="1" max="1" width="65.54296875" style="7" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:1">
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="7" spans="1:1">
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="1:1">
+      <c r="B10" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="12" spans="1:1">
+      <c r="B11" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:1">
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="16" spans="1:1">
+      <c r="B15" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>56</v>
       </c>
@@ -5758,131 +6942,2060 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F88E12-0893-4CEC-BFBC-DD16A056FE29}">
-  <dimension ref="A1"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7319914-46A4-47F2-A8A6-AEA4C0E88F7D}">
+  <dimension ref="A1:A41"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
-  <sheetData/>
+  <cols>
+    <col min="1" max="1" width="219.81640625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" ht="17.5">
+      <c r="A3" s="12" t="s">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="30"/>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="31" t="s">
+        <v>668</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="31" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="31" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="31" t="s">
+        <v>671</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="31" t="s">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" ht="17.5">
+      <c r="A11" s="12" t="s">
+        <v>673</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="30"/>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="30" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="30" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="30" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="31" t="s">
+        <v>677</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1" ht="17.5">
+      <c r="A18" s="12" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="30"/>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="31" t="s">
+        <v>679</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="31" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1" ht="17.5">
+      <c r="A23" s="12" t="s">
+        <v>681</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="30"/>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25" s="31" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26" s="31" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1" ht="17.5">
+      <c r="A28" s="12" t="s">
+        <v>684</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29" s="30"/>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30" s="31" t="s">
+        <v>685</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31" s="31" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32" s="31" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33" s="31" t="s">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1" ht="17.5">
+      <c r="A35" s="12" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36" s="30"/>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37" s="31" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38" s="31" t="s">
+        <v>691</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39" s="31" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41" t="s">
+        <v>693</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A66BB763-6A05-4319-A9B7-2B9C492F9961}">
+  <dimension ref="A1:A24"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="147.90625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" s="33" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2" s="33" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" s="33" t="s">
+        <v>696</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" s="33" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" s="33" t="s">
+        <v>698</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" s="33" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7" s="33" t="s">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" s="33" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" s="33" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" s="33" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" s="33" t="s">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" s="33" t="s">
+        <v>705</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" s="33" t="s">
+        <v>706</v>
+      </c>
+    </row>
+    <row r="14" spans="1:1">
+      <c r="A14" s="33" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" s="33" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="16" spans="1:1">
+      <c r="A16" s="33" t="s">
+        <v>709</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17" s="33" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18" s="33" t="s">
+        <v>711</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19" s="33" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20" s="33" t="s">
+        <v>713</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21" s="33" t="s">
+        <v>714</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22" s="33" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23" s="33" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24" s="32"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{10F88E12-0893-4CEC-BFBC-DD16A056FE29}">
+  <dimension ref="A1:B324"/>
+  <sheetFormatPr defaultRowHeight="14.5"/>
+  <cols>
+    <col min="2" max="2" width="68.26953125" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1">
+        <v>1</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:1">
+      <c r="A17">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="18" spans="1:1">
+      <c r="A18">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="19" spans="1:1">
+      <c r="A19">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="20" spans="1:1">
+      <c r="A20">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="21" spans="1:1">
+      <c r="A21">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="22" spans="1:1">
+      <c r="A22">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="23" spans="1:1">
+      <c r="A23">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="24" spans="1:1">
+      <c r="A24">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="1:1">
+      <c r="A25">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26" spans="1:1">
+      <c r="A26">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="27" spans="1:1">
+      <c r="A27">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="28" spans="1:1">
+      <c r="A28">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="29" spans="1:1">
+      <c r="A29">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="30" spans="1:1">
+      <c r="A30">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="31" spans="1:1">
+      <c r="A31">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="32" spans="1:1">
+      <c r="A32">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1">
+      <c r="A33">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:1">
+      <c r="A34">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="35" spans="1:1">
+      <c r="A35">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1">
+      <c r="A36">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="37" spans="1:1">
+      <c r="A37">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="38" spans="1:1">
+      <c r="A38">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="39" spans="1:1">
+      <c r="A39">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="40" spans="1:1">
+      <c r="A40">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="41" spans="1:1">
+      <c r="A41">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="42" spans="1:1">
+      <c r="A42">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="43" spans="1:1">
+      <c r="A43">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="44" spans="1:1">
+      <c r="A44">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="45" spans="1:1">
+      <c r="A45">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="46" spans="1:1">
+      <c r="A46">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="47" spans="1:1">
+      <c r="A47">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="48" spans="1:1">
+      <c r="A48">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="49" spans="1:1">
+      <c r="A49">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="50" spans="1:1">
+      <c r="A50">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="51" spans="1:1">
+      <c r="A51">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="52" spans="1:1">
+      <c r="A52">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="53" spans="1:1">
+      <c r="A53">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="54" spans="1:1">
+      <c r="A54">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="55" spans="1:1">
+      <c r="A55">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="56" spans="1:1">
+      <c r="A56">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="57" spans="1:1">
+      <c r="A57">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="58" spans="1:1">
+      <c r="A58">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="59" spans="1:1">
+      <c r="A59">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:1">
+      <c r="A60">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:1">
+      <c r="A61">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="62" spans="1:1">
+      <c r="A62">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="63" spans="1:1">
+      <c r="A63">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="64" spans="1:1">
+      <c r="A64">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="70" spans="1:1">
+      <c r="A70">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="71" spans="1:1">
+      <c r="A71">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="72" spans="1:1">
+      <c r="A72">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="73" spans="1:1">
+      <c r="A73">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="74" spans="1:1">
+      <c r="A74">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="75" spans="1:1">
+      <c r="A75">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="76" spans="1:1">
+      <c r="A76">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="77" spans="1:1">
+      <c r="A77">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="78" spans="1:1">
+      <c r="A78">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="79" spans="1:1">
+      <c r="A79">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="80" spans="1:1">
+      <c r="A80">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="81" spans="1:1">
+      <c r="A81">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="82" spans="1:1">
+      <c r="A82">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="83" spans="1:1">
+      <c r="A83">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="84" spans="1:1">
+      <c r="A84">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="85" spans="1:1">
+      <c r="A85">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="86" spans="1:1">
+      <c r="A86">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="87" spans="1:1">
+      <c r="A87">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="88" spans="1:1">
+      <c r="A88">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="89" spans="1:1">
+      <c r="A89">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="90" spans="1:1">
+      <c r="A90">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="91" spans="1:1">
+      <c r="A91">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="92" spans="1:1">
+      <c r="A92">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="93" spans="1:1">
+      <c r="A93">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="94" spans="1:1">
+      <c r="A94">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="95" spans="1:1">
+      <c r="A95">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="96" spans="1:1">
+      <c r="A96">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="97" spans="1:1">
+      <c r="A97">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="98" spans="1:1">
+      <c r="A98">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="99" spans="1:1">
+      <c r="A99">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="100" spans="1:1">
+      <c r="A100">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="101" spans="1:1">
+      <c r="A101">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="102" spans="1:1">
+      <c r="A102">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="103" spans="1:1">
+      <c r="A103">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="104" spans="1:1">
+      <c r="A104">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="105" spans="1:1">
+      <c r="A105">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="106" spans="1:1">
+      <c r="A106">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="107" spans="1:1">
+      <c r="A107">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="108" spans="1:1">
+      <c r="A108">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="109" spans="1:1">
+      <c r="A109">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="110" spans="1:1">
+      <c r="A110">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="111" spans="1:1">
+      <c r="A111">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="112" spans="1:1">
+      <c r="A112">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="113" spans="1:1">
+      <c r="A113">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="114" spans="1:1">
+      <c r="A114">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="115" spans="1:1">
+      <c r="A115">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="116" spans="1:1">
+      <c r="A116">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="117" spans="1:1">
+      <c r="A117">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="118" spans="1:1">
+      <c r="A118">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="119" spans="1:1">
+      <c r="A119">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="120" spans="1:1">
+      <c r="A120">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="121" spans="1:1">
+      <c r="A121">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="122" spans="1:1">
+      <c r="A122">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="123" spans="1:1">
+      <c r="A123">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="124" spans="1:1">
+      <c r="A124">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="125" spans="1:1">
+      <c r="A125">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="126" spans="1:1">
+      <c r="A126">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="127" spans="1:1">
+      <c r="A127">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="128" spans="1:1">
+      <c r="A128">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="129" spans="1:1">
+      <c r="A129">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="130" spans="1:1">
+      <c r="A130">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="131" spans="1:1">
+      <c r="A131">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="132" spans="1:1">
+      <c r="A132">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="133" spans="1:1">
+      <c r="A133">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="134" spans="1:1">
+      <c r="A134">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="135" spans="1:1">
+      <c r="A135">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="136" spans="1:1">
+      <c r="A136">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="137" spans="1:1">
+      <c r="A137">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="138" spans="1:1">
+      <c r="A138">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="139" spans="1:1">
+      <c r="A139">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="140" spans="1:1">
+      <c r="A140">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="141" spans="1:1">
+      <c r="A141">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="142" spans="1:1">
+      <c r="A142">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="143" spans="1:1">
+      <c r="A143">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="144" spans="1:1">
+      <c r="A144">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="145" spans="1:1">
+      <c r="A145">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="146" spans="1:1">
+      <c r="A146">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="147" spans="1:1">
+      <c r="A147">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="148" spans="1:1">
+      <c r="A148">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="149" spans="1:1">
+      <c r="A149">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="150" spans="1:1">
+      <c r="A150">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="151" spans="1:1">
+      <c r="A151">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="152" spans="1:1">
+      <c r="A152">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="153" spans="1:1">
+      <c r="A153">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="154" spans="1:1">
+      <c r="A154">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="155" spans="1:1">
+      <c r="A155">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="156" spans="1:1">
+      <c r="A156">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="157" spans="1:1">
+      <c r="A157">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="158" spans="1:1">
+      <c r="A158">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="159" spans="1:1">
+      <c r="A159">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="160" spans="1:1">
+      <c r="A160">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="161" spans="1:1">
+      <c r="A161">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="162" spans="1:1">
+      <c r="A162">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="163" spans="1:1">
+      <c r="A163">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="164" spans="1:1">
+      <c r="A164">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="165" spans="1:1">
+      <c r="A165">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="166" spans="1:1">
+      <c r="A166">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="167" spans="1:1">
+      <c r="A167">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:1">
+      <c r="A168">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="169" spans="1:1">
+      <c r="A169">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="170" spans="1:1">
+      <c r="A170">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="171" spans="1:1">
+      <c r="A171">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="172" spans="1:1">
+      <c r="A172">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="173" spans="1:1">
+      <c r="A173">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="174" spans="1:1">
+      <c r="A174">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="175" spans="1:1">
+      <c r="A175">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="176" spans="1:1">
+      <c r="A176">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="177" spans="1:1">
+      <c r="A177">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="178" spans="1:1">
+      <c r="A178">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="179" spans="1:1">
+      <c r="A179">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="180" spans="1:1">
+      <c r="A180">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="181" spans="1:1">
+      <c r="A181">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="182" spans="1:1">
+      <c r="A182">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="183" spans="1:1">
+      <c r="A183">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="184" spans="1:1">
+      <c r="A184">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="185" spans="1:1">
+      <c r="A185">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="186" spans="1:1">
+      <c r="A186">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="187" spans="1:1">
+      <c r="A187">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="188" spans="1:1">
+      <c r="A188">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="189" spans="1:1">
+      <c r="A189">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="190" spans="1:1">
+      <c r="A190">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="191" spans="1:1">
+      <c r="A191">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="192" spans="1:1">
+      <c r="A192">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="193" spans="1:1">
+      <c r="A193">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="194" spans="1:1">
+      <c r="A194">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="195" spans="1:1">
+      <c r="A195">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="196" spans="1:1">
+      <c r="A196">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="197" spans="1:1">
+      <c r="A197">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="198" spans="1:1">
+      <c r="A198">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="199" spans="1:1">
+      <c r="A199">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="200" spans="1:1">
+      <c r="A200">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="201" spans="1:1">
+      <c r="A201">
+        <v>201</v>
+      </c>
+    </row>
+    <row r="202" spans="1:1">
+      <c r="A202">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="203" spans="1:1">
+      <c r="A203">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="204" spans="1:1">
+      <c r="A204">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="205" spans="1:1">
+      <c r="A205">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="206" spans="1:1">
+      <c r="A206">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="207" spans="1:1">
+      <c r="A207">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="208" spans="1:1">
+      <c r="A208">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="209" spans="1:1">
+      <c r="A209">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="210" spans="1:1">
+      <c r="A210">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="211" spans="1:1">
+      <c r="A211">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="212" spans="1:1">
+      <c r="A212">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="213" spans="1:1">
+      <c r="A213">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="214" spans="1:1">
+      <c r="A214">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="215" spans="1:1">
+      <c r="A215">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="216" spans="1:1">
+      <c r="A216">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="217" spans="1:1">
+      <c r="A217">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="218" spans="1:1">
+      <c r="A218">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="219" spans="1:1">
+      <c r="A219">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="220" spans="1:1">
+      <c r="A220">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="221" spans="1:1">
+      <c r="A221">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="222" spans="1:1">
+      <c r="A222">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="223" spans="1:1">
+      <c r="A223">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="224" spans="1:1">
+      <c r="A224">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="225" spans="1:1">
+      <c r="A225">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="226" spans="1:1">
+      <c r="A226">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="227" spans="1:1">
+      <c r="A227">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="228" spans="1:1">
+      <c r="A228">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="229" spans="1:1">
+      <c r="A229">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="230" spans="1:1">
+      <c r="A230">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="231" spans="1:1">
+      <c r="A231">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="232" spans="1:1">
+      <c r="A232">
+        <v>232</v>
+      </c>
+    </row>
+    <row r="233" spans="1:1">
+      <c r="A233">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="234" spans="1:1">
+      <c r="A234">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="235" spans="1:1">
+      <c r="A235">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="236" spans="1:1">
+      <c r="A236">
+        <v>236</v>
+      </c>
+    </row>
+    <row r="237" spans="1:1">
+      <c r="A237">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="238" spans="1:1">
+      <c r="A238">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="239" spans="1:1">
+      <c r="A239">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="240" spans="1:1">
+      <c r="A240">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="241" spans="1:1">
+      <c r="A241">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="242" spans="1:1">
+      <c r="A242">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="243" spans="1:1">
+      <c r="A243">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="244" spans="1:1">
+      <c r="A244">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="245" spans="1:1">
+      <c r="A245">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="246" spans="1:1">
+      <c r="A246">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="247" spans="1:1">
+      <c r="A247">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="248" spans="1:1">
+      <c r="A248">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="249" spans="1:1">
+      <c r="A249">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="250" spans="1:1">
+      <c r="A250">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="251" spans="1:1">
+      <c r="A251">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="252" spans="1:1">
+      <c r="A252">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="253" spans="1:1">
+      <c r="A253">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="254" spans="1:1">
+      <c r="A254">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="255" spans="1:1">
+      <c r="A255">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="256" spans="1:1">
+      <c r="A256">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="257" spans="1:1">
+      <c r="A257">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="258" spans="1:1">
+      <c r="A258">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="259" spans="1:1">
+      <c r="A259">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="260" spans="1:1">
+      <c r="A260">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="261" spans="1:1">
+      <c r="A261">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="262" spans="1:1">
+      <c r="A262">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="263" spans="1:1">
+      <c r="A263">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="264" spans="1:1">
+      <c r="A264">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="265" spans="1:1">
+      <c r="A265">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="266" spans="1:1">
+      <c r="A266">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="267" spans="1:1">
+      <c r="A267">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="268" spans="1:1">
+      <c r="A268">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="269" spans="1:1">
+      <c r="A269">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="270" spans="1:1">
+      <c r="A270">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="271" spans="1:1">
+      <c r="A271">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="272" spans="1:1">
+      <c r="A272">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="273" spans="1:1">
+      <c r="A273">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="274" spans="1:1">
+      <c r="A274">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="275" spans="1:1">
+      <c r="A275">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="276" spans="1:1">
+      <c r="A276">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="277" spans="1:1">
+      <c r="A277">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="278" spans="1:1">
+      <c r="A278">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="279" spans="1:1">
+      <c r="A279">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="280" spans="1:1">
+      <c r="A280">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="281" spans="1:1">
+      <c r="A281">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="282" spans="1:1">
+      <c r="A282">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="283" spans="1:1">
+      <c r="A283">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="284" spans="1:1">
+      <c r="A284">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="285" spans="1:1">
+      <c r="A285">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="286" spans="1:1">
+      <c r="A286">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="287" spans="1:1">
+      <c r="A287">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="288" spans="1:1">
+      <c r="A288">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="289" spans="1:1">
+      <c r="A289">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="290" spans="1:1">
+      <c r="A290">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="291" spans="1:1">
+      <c r="A291">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="292" spans="1:1">
+      <c r="A292">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="293" spans="1:1">
+      <c r="A293">
+        <v>293</v>
+      </c>
+    </row>
+    <row r="294" spans="1:1">
+      <c r="A294">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="295" spans="1:1">
+      <c r="A295">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="296" spans="1:1">
+      <c r="A296">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="297" spans="1:1">
+      <c r="A297">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="298" spans="1:1">
+      <c r="A298">
+        <v>298</v>
+      </c>
+    </row>
+    <row r="299" spans="1:1">
+      <c r="A299">
+        <v>299</v>
+      </c>
+    </row>
+    <row r="300" spans="1:1">
+      <c r="A300">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="301" spans="1:1">
+      <c r="A301">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="302" spans="1:1">
+      <c r="A302">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="303" spans="1:1">
+      <c r="A303">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="304" spans="1:1">
+      <c r="A304">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="305" spans="1:1">
+      <c r="A305">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="306" spans="1:1">
+      <c r="A306">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="307" spans="1:1">
+      <c r="A307">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="308" spans="1:1">
+      <c r="A308">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="309" spans="1:1">
+      <c r="A309">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="310" spans="1:1">
+      <c r="A310">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="311" spans="1:1">
+      <c r="A311">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="312" spans="1:1">
+      <c r="A312">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="313" spans="1:1">
+      <c r="A313">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="314" spans="1:1">
+      <c r="A314">
+        <v>314</v>
+      </c>
+    </row>
+    <row r="315" spans="1:1">
+      <c r="A315">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="316" spans="1:1">
+      <c r="A316">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="317" spans="1:1">
+      <c r="A317">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="318" spans="1:1">
+      <c r="A318">
+        <v>318</v>
+      </c>
+    </row>
+    <row r="319" spans="1:1">
+      <c r="A319">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="320" spans="1:1">
+      <c r="A320">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="321" spans="1:1">
+      <c r="A321">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="322" spans="1:1">
+      <c r="A322">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="323" spans="1:1">
+      <c r="A323">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="324" spans="1:1">
+      <c r="A324">
+        <v>324</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62CBF515-27C6-4FD8-A46D-DA20D6347B92}">
   <dimension ref="A1:F49"/>
   <sheetFormatPr defaultRowHeight="14.5"/>
   <cols>
-    <col min="1" max="1" width="17.81640625" customWidth="1"/>
-    <col min="2" max="2" width="22.7265625" customWidth="1"/>
-    <col min="3" max="3" width="29.26953125" customWidth="1"/>
-    <col min="4" max="4" width="32.54296875" customWidth="1"/>
-    <col min="5" max="5" width="45.453125" customWidth="1"/>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="21.1796875" customWidth="1"/>
+    <col min="3" max="3" width="26.7265625" customWidth="1"/>
+    <col min="4" max="4" width="24.81640625" customWidth="1"/>
+    <col min="5" max="5" width="32.453125" customWidth="1"/>
     <col min="6" max="6" width="20.26953125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="21" t="s">
         <v>548</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="22" t="s">
         <v>549</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="22" t="s">
         <v>550</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="22" t="s">
         <v>551</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="23" t="s">
         <v>552</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="29">
-      <c r="A2" s="10" t="s">
+    <row r="2" spans="1:6" ht="26">
+      <c r="A2" s="24" t="s">
         <v>553</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="20" t="s">
         <v>554</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="20" t="s">
         <v>555</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="20" t="s">
         <v>556</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="25" t="s">
         <v>557</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="29">
-      <c r="A3" s="10" t="s">
+    <row r="3" spans="1:6" ht="26">
+      <c r="A3" s="24" t="s">
         <v>558</v>
       </c>
-      <c r="B3" s="6" t="s">
+      <c r="B3" s="20" t="s">
         <v>559</v>
       </c>
-      <c r="C3" s="6" t="s">
+      <c r="C3" s="20" t="s">
         <v>560</v>
       </c>
-      <c r="D3" s="6" t="s">
+      <c r="D3" s="20" t="s">
         <v>561</v>
       </c>
-      <c r="E3" s="6" t="s">
+      <c r="E3" s="25" t="s">
         <v>562</v>
       </c>
     </row>
-    <row r="4" spans="1:6" ht="29">
-      <c r="A4" s="10" t="s">
+    <row r="4" spans="1:6" ht="26">
+      <c r="A4" s="24" t="s">
         <v>563</v>
       </c>
-      <c r="B4" s="6" t="s">
+      <c r="B4" s="20" t="s">
         <v>564</v>
       </c>
-      <c r="C4" s="6" t="s">
+      <c r="C4" s="20" t="s">
         <v>564</v>
       </c>
-      <c r="D4" s="6" t="s">
+      <c r="D4" s="20" t="s">
         <v>565</v>
       </c>
-      <c r="E4" s="6" t="s">
+      <c r="E4" s="25" t="s">
         <v>566</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="29">
-      <c r="A5" s="10" t="s">
+    <row r="5" spans="1:6" ht="26">
+      <c r="A5" s="24" t="s">
         <v>567</v>
       </c>
-      <c r="B5" s="6" t="s">
+      <c r="B5" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="C5" s="6" t="s">
+      <c r="C5" s="20" t="s">
         <v>568</v>
       </c>
-      <c r="D5" s="6" t="s">
+      <c r="D5" s="20" t="s">
         <v>569</v>
       </c>
-      <c r="E5" s="6" t="s">
+      <c r="E5" s="25" t="s">
         <v>570</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="29">
-      <c r="A6" s="10" t="s">
+    <row r="6" spans="1:6" ht="26">
+      <c r="A6" s="24" t="s">
         <v>571</v>
       </c>
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="20" t="s">
         <v>572</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="20" t="s">
         <v>572</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="20" t="s">
         <v>573</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="25" t="s">
         <v>574</v>
       </c>
     </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="10" t="s">
+    <row r="7" spans="1:6" ht="26">
+      <c r="A7" s="24" t="s">
         <v>575</v>
       </c>
       <c r="B7" s="11" t="s">
@@ -5894,86 +9007,86 @@
       <c r="D7" s="11" t="s">
         <v>578</v>
       </c>
-      <c r="E7" s="11" t="s">
+      <c r="E7" s="26" t="s">
         <v>579</v>
       </c>
     </row>
-    <row r="8" spans="1:6" ht="29">
-      <c r="A8" s="10" t="s">
+    <row r="8" spans="1:6" ht="39">
+      <c r="A8" s="24" t="s">
         <v>580</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="20" t="s">
         <v>581</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="20" t="s">
         <v>582</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="20" t="s">
         <v>583</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="25" t="s">
         <v>584</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="29">
-      <c r="A9" s="10" t="s">
+    <row r="9" spans="1:6" ht="26">
+      <c r="A9" s="24" t="s">
         <v>585</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="20" t="s">
         <v>586</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="20" t="s">
         <v>587</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="20" t="s">
+        <v>663</v>
+      </c>
+      <c r="E9" s="25" t="s">
+        <v>664</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="26">
+      <c r="A10" s="24" t="s">
         <v>588</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="B10" s="20" t="s">
         <v>589</v>
       </c>
-    </row>
-    <row r="10" spans="1:6" ht="29">
-      <c r="A10" s="10" t="s">
+      <c r="C10" s="20" t="s">
+        <v>589</v>
+      </c>
+      <c r="D10" s="20" t="s">
         <v>590</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="E10" s="25" t="s">
         <v>591</v>
       </c>
-      <c r="C10" s="6" t="s">
-        <v>591</v>
-      </c>
-      <c r="D10" s="6" t="s">
+    </row>
+    <row r="11" spans="1:6" ht="26.5" thickBot="1">
+      <c r="A11" s="27" t="s">
         <v>592</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="B11" s="28" t="s">
         <v>593</v>
       </c>
-    </row>
-    <row r="11" spans="1:6" ht="29">
-      <c r="A11" s="10" t="s">
+      <c r="C11" s="28" t="s">
         <v>594</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="D11" s="28" t="s">
         <v>595</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="E11" s="29" t="s">
         <v>596</v>
-      </c>
-      <c r="D11" s="6" t="s">
-        <v>597</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>598</v>
       </c>
     </row>
     <row r="14" spans="1:6" ht="17.5">
       <c r="A14" s="12" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="16" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B16" s="16" t="s">
         <v>549</v>
@@ -5988,127 +9101,127 @@
         <v>552</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="17" spans="1:6" ht="29">
       <c r="A17" s="17" t="s">
+        <v>600</v>
+      </c>
+      <c r="B17" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="C17" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="D17" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="E17" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="F17" s="6" t="s">
         <v>602</v>
-      </c>
-      <c r="B17" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="C17" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="D17" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="E17" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="F17" s="6" t="s">
-        <v>604</v>
       </c>
     </row>
     <row r="18" spans="1:6" ht="29">
       <c r="A18" s="17" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C18" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D18" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="19" spans="1:6" ht="29">
       <c r="A19" s="17" t="s">
+        <v>605</v>
+      </c>
+      <c r="B19" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="C19" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="D19" s="18" t="s">
+        <v>606</v>
+      </c>
+      <c r="E19" s="18" t="s">
+        <v>606</v>
+      </c>
+      <c r="F19" s="6" t="s">
         <v>607</v>
-      </c>
-      <c r="B19" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="C19" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="D19" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="E19" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>609</v>
       </c>
     </row>
     <row r="20" spans="1:6" ht="29">
       <c r="A20" s="17" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="B20" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C20" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="D20" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E20" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F20" s="6" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="21" spans="1:6">
       <c r="A21" s="17" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B21" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C21" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D21" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E21" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F21" s="6" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
     </row>
     <row r="22" spans="1:6">
       <c r="A22" s="17" t="s">
+        <v>612</v>
+      </c>
+      <c r="B22" s="18" t="s">
+        <v>613</v>
+      </c>
+      <c r="C22" s="18" t="s">
         <v>614</v>
       </c>
-      <c r="B22" s="18" t="s">
+      <c r="D22" s="18" t="s">
         <v>615</v>
       </c>
-      <c r="C22" s="18" t="s">
+      <c r="E22" s="18" t="s">
         <v>616</v>
       </c>
-      <c r="D22" s="18" t="s">
+      <c r="F22" s="6" t="s">
         <v>617</v>
-      </c>
-      <c r="E22" s="18" t="s">
-        <v>618</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>619</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -6127,12 +9240,12 @@
     </row>
     <row r="26" spans="1:6" ht="17.5">
       <c r="A26" s="12" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
     </row>
     <row r="28" spans="1:6">
       <c r="A28" s="16" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B28" s="16" t="s">
         <v>549</v>
@@ -6147,430 +9260,431 @@
         <v>552</v>
       </c>
       <c r="F28" s="13" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
     </row>
     <row r="29" spans="1:6" ht="29">
       <c r="A29" s="17" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="B29" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C29" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D29" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E29" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F29" s="6" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="29">
       <c r="A30" s="17" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="B30" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C30" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D30" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E30" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F30" s="6" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
     </row>
     <row r="31" spans="1:6">
       <c r="A31" s="17" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="B31" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C31" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D31" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E31" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F31" s="6" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
     </row>
     <row r="32" spans="1:6" ht="29">
       <c r="A32" s="17" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="B32" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C32" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D32" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F32" s="6" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
     </row>
     <row r="33" spans="1:6" ht="29">
       <c r="A33" s="17" t="s">
+        <v>627</v>
+      </c>
+      <c r="B33" s="18" t="s">
+        <v>601</v>
+      </c>
+      <c r="C33" s="18" t="s">
+        <v>606</v>
+      </c>
+      <c r="D33" s="18" t="s">
+        <v>628</v>
+      </c>
+      <c r="E33" s="18" t="s">
         <v>629</v>
       </c>
-      <c r="B33" s="18" t="s">
-        <v>603</v>
-      </c>
-      <c r="C33" s="18" t="s">
-        <v>608</v>
-      </c>
-      <c r="D33" s="18" t="s">
+      <c r="F33" s="6" t="s">
         <v>630</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>631</v>
-      </c>
-      <c r="F33" s="6" t="s">
-        <v>632</v>
       </c>
     </row>
     <row r="34" spans="1:6">
       <c r="A34" s="17" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="B34" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C34" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D34" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
     </row>
     <row r="35" spans="1:6" ht="29">
       <c r="A35" s="19" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="B35" s="19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C35" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D35" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E35" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F35" s="10" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
     </row>
     <row r="36" spans="1:6">
       <c r="A36" s="17" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="B36" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="C36" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D36" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F36" s="6" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
     </row>
     <row r="37" spans="1:6">
       <c r="A37" s="17" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="B37" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C37" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D37" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F37" s="6" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="29">
       <c r="A38" s="17" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="B38" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C38" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D38" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F38" s="6" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
     </row>
     <row r="39" spans="1:6" ht="29">
       <c r="A39" s="17" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="B39" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C39" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D39" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F39" s="6" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
     </row>
     <row r="40" spans="1:6">
       <c r="A40" s="17" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="B40" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C40" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D40" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F40" s="6" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
     </row>
     <row r="41" spans="1:6" ht="29">
       <c r="A41" s="17" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="B41" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C41" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D41" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F41" s="6" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
     </row>
     <row r="42" spans="1:6" ht="29">
       <c r="A42" s="19" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="B42" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C42" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F42" s="10" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
     </row>
     <row r="43" spans="1:6" ht="29">
       <c r="A43" s="17" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="B43" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C43" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D43" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="F43" s="6" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
     </row>
     <row r="44" spans="1:6">
       <c r="A44" s="17" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="B44" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C44" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D44" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F44" s="6" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="29">
       <c r="A45" s="17" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="B45" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C45" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D45" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F45" s="6" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="17" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="B46" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C46" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D46" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F46" s="6" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
     </row>
     <row r="47" spans="1:6" ht="29">
       <c r="A47" s="17" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="B47" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C47" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D47" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F47" s="6" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
     </row>
     <row r="48" spans="1:6">
       <c r="A48" s="17" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="B48" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C48" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D48" s="18" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F48" s="6" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
     </row>
     <row r="49" spans="1:6" ht="29">
       <c r="A49" s="19" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="B49" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="C49" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="D49" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="E49" s="19" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="F49" s="10" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
 </worksheet>
 </file>